--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-picarro.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-picarro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E335DA09-EAE0-48DF-8CF2-D84D5AE7A421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FCF534-81EE-4C5B-9727-6F16681AD814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,6 +39,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={7AD64863-29D3-4A3A-9CB4-FF995EA1C8F1}</author>
+    <author>tc={9ADA5EE6-9A05-4588-AEE1-6BA3F17D6A75}</author>
     <author>tc={C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}</author>
   </authors>
   <commentList>
@@ -50,12 +51,20 @@
     Standard liters per minute</t>
       </text>
     </comment>
-    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}">
+    <comment ref="M2" authorId="1" shapeId="0" xr:uid="{9ADA5EE6-9A05-4588-AEE1-6BA3F17D6A75}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Samples are blocked and then randomized within the blocks</t>
+    Same timeframe as picarro 2 h delay in compared to real time, sommertime?</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="2" shapeId="0" xr:uid="{C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Samples are blocked, then randomized within the blocks</t>
       </text>
     </comment>
   </commentList>
@@ -63,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
   <si>
     <t>Valve code</t>
   </si>
@@ -95,9 +104,6 @@
     <t>Q  Bypass end [SL/min]</t>
   </si>
   <si>
-    <t>endtime Piccarro</t>
-  </si>
-  <si>
     <t>enddate</t>
   </si>
   <si>
@@ -117,6 +123,15 @@
   </si>
   <si>
     <t>Qsum_start [SL/min]</t>
+  </si>
+  <si>
+    <t>Qsum_end</t>
+  </si>
+  <si>
+    <t>Qmean [SL/min]</t>
+  </si>
+  <si>
+    <t>2026-04-14-08:02</t>
   </si>
 </sst>
 </file>
@@ -126,7 +141,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +154,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -481,8 +502,11 @@
   <threadedComment ref="F1" dT="2026-03-12T10:45:59.68" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{7AD64863-29D3-4A3A-9CB4-FF995EA1C8F1}">
     <text>Standard liters per minute</text>
   </threadedComment>
+  <threadedComment ref="M2" dT="2026-04-15T09:34:47.80" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{9ADA5EE6-9A05-4588-AEE1-6BA3F17D6A75}">
+    <text>Same timeframe as picarro 2 h delay in compared to real time, sommertime?</text>
+  </threadedComment>
   <threadedComment ref="D5" dT="2026-04-15T09:15:29.59" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}">
-    <text>Samples are blocked and then randomized within the blocks</text>
+    <text>Samples are blocked, then randomized within the blocks</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -528,7 +552,7 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
@@ -536,14 +560,17 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="M1" t="s">
         <v>5</v>
       </c>
       <c r="N1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -557,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1">
         <v>2.0190000000000001</v>
@@ -572,9 +599,17 @@
         <f>F2+G2</f>
         <v>1.1739999999999999</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="2"/>
+      <c r="K2" s="1">
+        <f>I2+J2</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="1">
+        <f>AVERAGE(H2,K2)</f>
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -588,7 +623,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1">
         <v>2.0390000000000001</v>
@@ -604,8 +639,14 @@
         <v>1.173</v>
       </c>
       <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="K3" s="1">
+        <f t="shared" ref="K3:K25" si="1">I3+J3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:L25" si="2">AVERAGE(H3,K3)</f>
+        <v>0.58650000000000002</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -618,7 +659,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1">
         <v>2.137</v>
@@ -634,8 +675,14 @@
         <v>1.1739999999999999</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="K4" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58699999999999997</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -648,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1">
         <v>2.1080000000000001</v>
@@ -663,8 +710,14 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="K5" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -677,7 +730,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <v>2.0569999999999999</v>
@@ -692,8 +745,14 @@
         <f t="shared" si="0"/>
         <v>1.1739999999999999</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58699999999999997</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -703,10 +762,10 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="10">
@@ -719,8 +778,14 @@
         <f t="shared" si="0"/>
         <v>1.1819999999999999</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="K7" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="2"/>
+        <v>0.59099999999999997</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -733,7 +798,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1">
         <v>2.0089999999999999</v>
@@ -749,8 +814,14 @@
         <v>1.175</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="K8" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -763,7 +834,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
         <v>2.0390000000000001</v>
@@ -779,8 +850,14 @@
         <v>1.175</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="K9" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -793,7 +870,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="1">
         <v>2.2909999999999999</v>
@@ -808,8 +885,14 @@
         <f t="shared" si="0"/>
         <v>1.173</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="K10" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58650000000000002</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -822,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1">
         <v>2.0699999999999998</v>
@@ -838,8 +921,14 @@
         <v>1.1719999999999999</v>
       </c>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="K11" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58599999999999997</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -852,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1">
         <v>2.1829999999999998</v>
@@ -868,8 +957,14 @@
         <v>1.1759999999999999</v>
       </c>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="K12" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58799999999999997</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -879,10 +974,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="10">
@@ -896,8 +991,14 @@
         <v>1.179</v>
       </c>
       <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="K13" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58950000000000002</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -910,7 +1011,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1">
         <v>2.024</v>
@@ -926,8 +1027,14 @@
         <v>1.173</v>
       </c>
       <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="K14" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58650000000000002</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -940,7 +1047,7 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1">
         <v>2.0830000000000002</v>
@@ -956,8 +1063,14 @@
         <v>1.1739999999999999</v>
       </c>
       <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="K15" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58699999999999997</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -970,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1">
         <v>2.04</v>
@@ -986,8 +1099,14 @@
         <v>1.173</v>
       </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="K16" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58650000000000002</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
@@ -1000,7 +1119,7 @@
         <v>14</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1">
         <v>2.0569999999999999</v>
@@ -1016,8 +1135,14 @@
         <v>1.175</v>
       </c>
       <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="K17" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -1030,7 +1155,7 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1">
         <v>2.093</v>
@@ -1046,8 +1171,14 @@
         <v>1.175</v>
       </c>
       <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="K18" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19">
@@ -1057,10 +1188,10 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="10">
@@ -1074,8 +1205,14 @@
         <v>1.1830000000000001</v>
       </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="K19" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <f t="shared" si="2"/>
+        <v>0.59150000000000003</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20">
@@ -1088,7 +1225,7 @@
         <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" s="1">
         <v>2.0859999999999999</v>
@@ -1104,8 +1241,14 @@
         <v>1.177</v>
       </c>
       <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="K20" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58850000000000002</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21">
@@ -1118,7 +1261,7 @@
         <v>17</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1">
         <v>2.1190000000000002</v>
@@ -1134,8 +1277,14 @@
         <v>1.175</v>
       </c>
       <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="K21" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22">
@@ -1148,7 +1297,7 @@
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1">
         <v>2.036</v>
@@ -1164,8 +1313,14 @@
         <v>1.175</v>
       </c>
       <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="K22" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
@@ -1178,7 +1333,7 @@
         <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1">
         <v>2.0550000000000002</v>
@@ -1194,8 +1349,14 @@
         <v>1.175</v>
       </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="K23" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58750000000000002</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
@@ -1208,7 +1369,7 @@
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1">
         <v>2.073</v>
@@ -1224,8 +1385,14 @@
         <v>1.179</v>
       </c>
       <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="K24" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="2"/>
+        <v>0.58950000000000002</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
@@ -1235,10 +1402,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="11">
@@ -1252,8 +1419,14 @@
         <v>1.1850000000000001</v>
       </c>
       <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="K25" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="2"/>
+        <v>0.59250000000000003</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F26" s="8"/>

--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-picarro.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-picarro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FCF534-81EE-4C5B-9727-6F16681AD814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4BDA01-FDBC-4AA5-8967-A146874D0BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -40,6 +40,7 @@
   <authors>
     <author>tc={7AD64863-29D3-4A3A-9CB4-FF995EA1C8F1}</author>
     <author>tc={9ADA5EE6-9A05-4588-AEE1-6BA3F17D6A75}</author>
+    <author>tc={BF11EDF2-477B-4F80-B063-70EFE97B9D08}</author>
     <author>tc={C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}</author>
   </authors>
   <commentList>
@@ -59,7 +60,15 @@
     Same timeframe as picarro 2 h delay in compared to real time, sommertime?</t>
       </text>
     </comment>
-    <comment ref="D5" authorId="2" shapeId="0" xr:uid="{C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}">
+    <comment ref="N2" authorId="2" shapeId="0" xr:uid="{BF11EDF2-477B-4F80-B063-70EFE97B9D08}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Last cyckle aprox 50 minite past this</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="3" shapeId="0" xr:uid="{C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -141,7 +150,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,12 +169,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -200,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -209,10 +212,8 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,6 +506,9 @@
   <threadedComment ref="M2" dT="2026-04-15T09:34:47.80" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{9ADA5EE6-9A05-4588-AEE1-6BA3F17D6A75}">
     <text>Same timeframe as picarro 2 h delay in compared to real time, sommertime?</text>
   </threadedComment>
+  <threadedComment ref="N2" dT="2026-04-21T07:03:15.54" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{BF11EDF2-477B-4F80-B063-70EFE97B9D08}">
+    <text>Last cyckle aprox 50 minite past this</text>
+  </threadedComment>
   <threadedComment ref="D5" dT="2026-04-15T09:15:29.59" personId="{CB8B1872-E8E1-48AA-8172-37FB038FBF21}" id="{C3A4F254-8AF7-4ABB-8EB5-C1032E8DF48D}">
     <text>Samples are blocked, then randomized within the blocks</text>
   </threadedComment>
@@ -513,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
@@ -589,7 +593,7 @@
       <c r="E2" s="1">
         <v>2.0190000000000001</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="1">
         <v>0.22500000000000001</v>
       </c>
       <c r="G2" s="1">
@@ -599,18 +603,26 @@
         <f>F2+G2</f>
         <v>1.1739999999999999</v>
       </c>
+      <c r="I2" s="1">
+        <v>0.219</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0.97099999999999997</v>
+      </c>
       <c r="K2" s="1">
-        <f>I2+J2</f>
-        <v>0</v>
+        <f>I5+J5</f>
+        <v>1.1759999999999999</v>
       </c>
       <c r="L2" s="1">
         <f>AVERAGE(H2,K2)</f>
-        <v>0.58699999999999997</v>
+        <v>1.1749999999999998</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="3"/>
+      <c r="N2" s="3">
+        <v>46132.074305555558</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -628,7 +640,7 @@
       <c r="E3" s="1">
         <v>2.0390000000000001</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G3" s="1">
@@ -638,14 +650,19 @@
         <f t="shared" ref="H3:H25" si="0">F3+G3</f>
         <v>1.173</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="I3" s="1">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.98</v>
+      </c>
       <c r="K3" s="1">
         <f t="shared" ref="K3:K25" si="1">I3+J3</f>
-        <v>0</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="L3" s="1">
         <f t="shared" ref="L3:L25" si="2">AVERAGE(H3,K3)</f>
-        <v>0.58650000000000002</v>
+        <v>1.1825000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -664,7 +681,7 @@
       <c r="E4" s="1">
         <v>2.137</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G4" s="1">
@@ -674,14 +691,19 @@
         <f t="shared" si="0"/>
         <v>1.1739999999999999</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="I4" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.0309999999999999</v>
+      </c>
       <c r="K4" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1909999999999998</v>
       </c>
       <c r="L4" s="1">
         <f t="shared" si="2"/>
-        <v>0.58699999999999997</v>
+        <v>1.1824999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -694,13 +716,13 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="1">
         <v>2.1080000000000001</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G5" s="1">
@@ -710,13 +732,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
+      <c r="I5" s="1">
+        <v>0.153</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.0229999999999999</v>
+      </c>
       <c r="K5" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1759999999999999</v>
       </c>
       <c r="L5" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1755</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -735,7 +763,7 @@
       <c r="E6" s="1">
         <v>2.0569999999999999</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G6" s="1">
@@ -745,13 +773,19 @@
         <f t="shared" si="0"/>
         <v>1.1739999999999999</v>
       </c>
+      <c r="I6" s="1">
+        <v>0.161</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.028</v>
+      </c>
       <c r="K6" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1890000000000001</v>
       </c>
       <c r="L6" s="1">
         <f t="shared" si="2"/>
-        <v>0.58699999999999997</v>
+        <v>1.1815</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -768,7 +802,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="10">
+      <c r="F7" s="1">
         <v>0.40799999999999997</v>
       </c>
       <c r="G7" s="1">
@@ -778,13 +812,19 @@
         <f t="shared" si="0"/>
         <v>1.1819999999999999</v>
       </c>
+      <c r="I7">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0.77200000000000002</v>
+      </c>
       <c r="K7" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1990000000000001</v>
       </c>
       <c r="L7" s="1">
         <f t="shared" si="2"/>
-        <v>0.59099999999999997</v>
+        <v>1.1905000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -803,7 +843,7 @@
       <c r="E8" s="1">
         <v>2.0089999999999999</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="1">
         <v>0.22500000000000001</v>
       </c>
       <c r="G8" s="1">
@@ -813,14 +853,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="I8" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
       <c r="K8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1825000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -839,7 +884,7 @@
       <c r="E9" s="1">
         <v>2.0390000000000001</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="1">
         <v>0.22700000000000001</v>
       </c>
       <c r="G9" s="1">
@@ -849,14 +894,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="I9" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0.99199999999999999</v>
+      </c>
       <c r="K9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1835</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -869,13 +919,13 @@
       <c r="C10">
         <v>8</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="1">
         <v>2.2909999999999999</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="1">
         <v>0.224</v>
       </c>
       <c r="G10" s="1">
@@ -885,13 +935,19 @@
         <f t="shared" si="0"/>
         <v>1.173</v>
       </c>
+      <c r="I10" s="1">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0.96899999999999997</v>
+      </c>
       <c r="K10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.194</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="2"/>
-        <v>0.58650000000000002</v>
+        <v>1.1835</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -910,7 +966,7 @@
       <c r="E11" s="1">
         <v>2.0699999999999998</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G11" s="1">
@@ -920,14 +976,19 @@
         <f t="shared" si="0"/>
         <v>1.1719999999999999</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="I11" s="1">
+        <v>0.217</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0.91500000000000004</v>
+      </c>
       <c r="K11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1320000000000001</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="2"/>
-        <v>0.58599999999999997</v>
+        <v>1.1520000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -946,7 +1007,7 @@
       <c r="E12" s="1">
         <v>2.1829999999999998</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G12" s="1">
@@ -956,14 +1017,19 @@
         <f t="shared" si="0"/>
         <v>1.1759999999999999</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="I12" s="1">
+        <v>0.215</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.97899999999999998</v>
+      </c>
       <c r="K12" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.194</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
-        <v>0.58799999999999997</v>
+        <v>1.1850000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -980,7 +1046,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="10">
+      <c r="F13" s="1">
         <v>0.40899999999999997</v>
       </c>
       <c r="G13" s="1">
@@ -990,14 +1056,19 @@
         <f t="shared" si="0"/>
         <v>1.179</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="I13" s="1">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.77200000000000002</v>
+      </c>
       <c r="K13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1990000000000001</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
-        <v>0.58950000000000002</v>
+        <v>1.1890000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1010,13 +1081,13 @@
       <c r="C14">
         <v>11</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="1">
         <v>2.024</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="1">
         <v>0.22700000000000001</v>
       </c>
       <c r="G14" s="1">
@@ -1026,14 +1097,19 @@
         <f t="shared" si="0"/>
         <v>1.173</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="I14" s="1">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.96599999999999997</v>
+      </c>
       <c r="K14" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1910000000000001</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
-        <v>0.58650000000000002</v>
+        <v>1.1819999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1052,7 +1128,7 @@
       <c r="E15" s="1">
         <v>2.0830000000000002</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G15" s="1">
@@ -1062,14 +1138,19 @@
         <f t="shared" si="0"/>
         <v>1.1739999999999999</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="I15" s="1">
+        <v>0.217</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.97899999999999998</v>
+      </c>
       <c r="K15" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.196</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
-        <v>0.58699999999999997</v>
+        <v>1.1850000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1088,7 +1169,7 @@
       <c r="E16" s="1">
         <v>2.04</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="1">
         <v>0.22500000000000001</v>
       </c>
       <c r="G16" s="1">
@@ -1098,14 +1179,19 @@
         <f t="shared" si="0"/>
         <v>1.173</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="I16" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1.0229999999999999</v>
+      </c>
       <c r="K16" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>I16+J16</f>
+        <v>1.6829999999999998</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
-        <v>0.58650000000000002</v>
+        <v>1.4279999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -1118,13 +1204,13 @@
       <c r="C17">
         <v>14</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="1">
         <v>2.0569999999999999</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="1">
         <v>0.22500000000000001</v>
       </c>
       <c r="G17" s="1">
@@ -1134,14 +1220,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="J17" s="1"/>
+      <c r="I17" s="1">
+        <v>0.223</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.97199999999999998</v>
+      </c>
       <c r="K17" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>I17+J17</f>
+        <v>1.1950000000000001</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1850000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -1160,7 +1251,7 @@
       <c r="E18" s="1">
         <v>2.093</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="1">
         <v>0.22500000000000001</v>
       </c>
       <c r="G18" s="1">
@@ -1170,14 +1261,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="J18" s="1"/>
+      <c r="I18" s="1">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.96499999999999997</v>
+      </c>
       <c r="K18" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1930000000000001</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1840000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -1194,7 +1290,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="10">
+      <c r="F19" s="1">
         <v>0.44800000000000001</v>
       </c>
       <c r="G19" s="1">
@@ -1204,14 +1300,19 @@
         <f t="shared" si="0"/>
         <v>1.1830000000000001</v>
       </c>
-      <c r="J19" s="1"/>
+      <c r="I19" s="1">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.72799999999999998</v>
+      </c>
       <c r="K19" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.202</v>
       </c>
       <c r="L19" s="1">
         <f t="shared" si="2"/>
-        <v>0.59150000000000003</v>
+        <v>1.1924999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1230,7 +1331,7 @@
       <c r="E20" s="1">
         <v>2.0859999999999999</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="1">
         <v>0.22700000000000001</v>
       </c>
       <c r="G20" s="1">
@@ -1240,14 +1341,19 @@
         <f t="shared" si="0"/>
         <v>1.177</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="I20" s="1">
+        <v>0.223</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.96799999999999997</v>
+      </c>
       <c r="K20" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1910000000000001</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" si="2"/>
-        <v>0.58850000000000002</v>
+        <v>1.1840000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1260,13 +1366,13 @@
       <c r="C21">
         <v>17</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E21" s="1">
         <v>2.1190000000000002</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="1">
         <v>0.22600000000000001</v>
       </c>
       <c r="G21" s="1">
@@ -1276,14 +1382,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="J21" s="1"/>
+      <c r="I21" s="1">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.96599999999999997</v>
+      </c>
       <c r="K21" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="L21" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1835</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1302,7 +1413,7 @@
       <c r="E22" s="1">
         <v>2.036</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="1">
         <v>0.22700000000000001</v>
       </c>
       <c r="G22" s="1">
@@ -1312,14 +1423,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="J22" s="1"/>
+      <c r="I22" s="1">
+        <v>0.219</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.97399999999999998</v>
+      </c>
       <c r="K22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1930000000000001</v>
       </c>
       <c r="L22" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1840000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -1338,7 +1454,7 @@
       <c r="E23" s="1">
         <v>2.0550000000000002</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="1">
         <v>0.22700000000000001</v>
       </c>
       <c r="G23" s="1">
@@ -1348,14 +1464,19 @@
         <f t="shared" si="0"/>
         <v>1.175</v>
       </c>
-      <c r="J23" s="1"/>
+      <c r="I23" s="1">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.96399999999999997</v>
+      </c>
       <c r="K23" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" si="2"/>
-        <v>0.58750000000000002</v>
+        <v>1.1835</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1374,7 +1495,7 @@
       <c r="E24" s="1">
         <v>2.073</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="1">
         <v>0.22700000000000001</v>
       </c>
       <c r="G24" s="1">
@@ -1384,14 +1505,19 @@
         <f t="shared" si="0"/>
         <v>1.179</v>
       </c>
-      <c r="J24" s="1"/>
+      <c r="I24" s="1">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.96399999999999997</v>
+      </c>
       <c r="K24" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1950000000000001</v>
       </c>
       <c r="L24" s="1">
         <f t="shared" si="2"/>
-        <v>0.58950000000000002</v>
+        <v>1.1870000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1408,7 +1534,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="11">
+      <c r="F25" s="9">
         <v>0.45300000000000001</v>
       </c>
       <c r="G25" s="1">
@@ -1418,18 +1544,20 @@
         <f t="shared" si="0"/>
         <v>1.1850000000000001</v>
       </c>
-      <c r="J25" s="1"/>
+      <c r="I25" s="1">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.72899999999999998</v>
+      </c>
       <c r="K25" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.202</v>
       </c>
       <c r="L25" s="1">
         <f t="shared" si="2"/>
-        <v>0.59250000000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="F26" s="8"/>
+        <v>1.1935</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-picarro.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-picarro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4BDA01-FDBC-4AA5-8967-A146874D0BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2C4096-4E72-4BCC-BBAB-B402968BE2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,7 +150,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,12 +163,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -203,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -213,7 +207,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,27 +795,27 @@
         <v>11</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="1">
+      <c r="F7" s="5">
         <v>0.40799999999999997</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="5">
         <v>0.77400000000000002</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="5">
         <f t="shared" si="0"/>
         <v>1.1819999999999999</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="4">
         <v>0.42699999999999999</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="5">
         <v>0.77200000000000002</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="5">
         <f t="shared" si="1"/>
         <v>1.1990000000000001</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="5">
         <f t="shared" si="2"/>
         <v>1.1905000000000001</v>
       </c>
@@ -1046,27 +1039,27 @@
         <v>11</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="1">
+      <c r="F13" s="5">
         <v>0.40899999999999997</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="5">
         <v>0.77</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="5">
         <f t="shared" si="0"/>
         <v>1.179</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="5">
         <v>0.42699999999999999</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="5">
         <v>0.77200000000000002</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="5">
         <f t="shared" si="1"/>
         <v>1.1990000000000001</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="5">
         <f t="shared" si="2"/>
         <v>1.1890000000000001</v>
       </c>
@@ -1290,27 +1283,27 @@
         <v>11</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="1">
+      <c r="F19" s="5">
         <v>0.44800000000000001</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="5">
         <v>0.73499999999999999</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="5">
         <f t="shared" si="0"/>
         <v>1.1830000000000001</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="5">
         <v>0.47399999999999998</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="5">
         <v>0.72799999999999998</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="5">
         <f t="shared" si="1"/>
         <v>1.202</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="5">
         <f t="shared" si="2"/>
         <v>1.1924999999999999</v>
       </c>
@@ -1534,27 +1527,27 @@
         <v>11</v>
       </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="9">
+      <c r="F25" s="7">
         <v>0.45300000000000001</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="5">
         <v>0.73199999999999998</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="5">
         <f t="shared" si="0"/>
         <v>1.1850000000000001</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="5">
         <v>0.47299999999999998</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="5">
         <v>0.72899999999999998</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="5">
         <f t="shared" si="1"/>
         <v>1.202</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="5">
         <f t="shared" si="2"/>
         <v>1.1935</v>
       </c>
